--- a/backend/data/input/trades/mapping copy 2.xlsx
+++ b/backend/data/input/trades/mapping copy 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/louisgarnier/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A38780-59C6-0F47-B632-A89E3FB0140B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F148152-AB59-3A4D-A9D1-A2579F0EA34C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{C2A2B53B-49A6-234D-B395-58C1E4ECDF9F}"/>
   </bookViews>
